--- a/artfynd/A 39503-2024 artfynd.xlsx
+++ b/artfynd/A 39503-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -897,6 +897,113 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120448428</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Blekatjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>470512</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7016776</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39503-2024 artfynd.xlsx
+++ b/artfynd/A 39503-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101537654</v>
+        <v>120639689</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Trusta - Rödön, Jmt</t>
+          <t>Blekatjärnen, Blekatjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>470309.9785594774</v>
+        <v>470367</v>
       </c>
       <c r="R2" t="n">
-        <v>7017015.767980784</v>
+        <v>7017041</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-06-07</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-06-07</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,27 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104036321</v>
+        <v>120641835</v>
       </c>
       <c r="B3" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rödön V, Jmt</t>
+          <t>Blekatjärnen, Blekatjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>470407.9130659044</v>
+        <v>470330</v>
       </c>
       <c r="R3" t="n">
-        <v>7016932.954981701</v>
+        <v>7017038</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-09-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-09-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,27 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120448428</v>
+        <v>120641044</v>
       </c>
       <c r="B4" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,37 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Blekatjärnen, Jmt</t>
+          <t>Blekatjärnen, Blekatjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>470512</v>
+        <v>470279</v>
       </c>
       <c r="R4" t="n">
-        <v>7016776</v>
+        <v>7017039</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,17 +954,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>På grov granlåga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,27 +989,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120641835</v>
+        <v>104036321</v>
       </c>
       <c r="B5" t="n">
-        <v>78628</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,37 +1012,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Blekatjärnen, Blekatjärnen, Jmt</t>
+          <t>Rödön V, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>470330</v>
+        <v>470408</v>
       </c>
       <c r="R5" t="n">
-        <v>7017038</v>
+        <v>7016933</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1076,22 +1066,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:25</t>
+          <t>2022-09-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:25</t>
+          <t>2022-09-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,49 +1086,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120639689</v>
+        <v>120639644</v>
       </c>
       <c r="B6" t="n">
-        <v>78628</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>470367</v>
+        <v>470361</v>
       </c>
       <c r="R6" t="n">
-        <v>7017041</v>
+        <v>7017017</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1193,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,55 +1205,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120641824</v>
+        <v>120641868</v>
       </c>
       <c r="B7" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Blekatjärnen, Blekatjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>470330</v>
+        <v>470335</v>
       </c>
       <c r="R7" t="n">
-        <v>7017038</v>
+        <v>7017030</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1310,7 +1275,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,12 +1285,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Barkfläkt gran. Typiska hackspår.</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,50 +1312,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120640895</v>
+        <v>101537654</v>
       </c>
       <c r="B8" t="n">
-        <v>100322</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Blekatjärnen, Blekatjärnen, Jmt</t>
+          <t>Trusta - Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>470279</v>
+        <v>470310</v>
       </c>
       <c r="R8" t="n">
-        <v>7017039</v>
+        <v>7017016</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,22 +1377,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:11</t>
+          <t>2022-06-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:11</t>
+          <t>2022-06-07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,27 +1397,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120641868</v>
+        <v>120640856</v>
       </c>
       <c r="B9" t="n">
-        <v>78594</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,7 +1444,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>470335</v>
+        <v>470308</v>
       </c>
       <c r="R9" t="n">
         <v>7017030</v>
@@ -1539,7 +1479,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1489,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt på gamla sälgar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,15 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120639552</v>
+        <v>120639534</v>
       </c>
       <c r="B10" t="n">
-        <v>100322</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,21 +1532,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1616,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>470404</v>
+        <v>470410</v>
       </c>
       <c r="R10" t="n">
-        <v>7017028</v>
+        <v>7017032</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1651,7 +1591,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1601,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,15 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120643646</v>
+        <v>120448428</v>
       </c>
       <c r="B11" t="n">
-        <v>57501</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1704,43 +1639,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Blekatjärnen, Blekatjärnen, Jmt</t>
+          <t>Blekatjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>470483</v>
+        <v>470512</v>
       </c>
       <c r="R11" t="n">
-        <v>7016835</v>
+        <v>7016776</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1767,22 +1693,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>14:44</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:44</t>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1797,62 +1718,62 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120639534</v>
+        <v>120641824</v>
       </c>
       <c r="B12" t="n">
-        <v>79704</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Blekatjärnen, Blekatjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>470410</v>
+        <v>470330</v>
       </c>
       <c r="R12" t="n">
-        <v>7017032</v>
+        <v>7017038</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1884,7 +1805,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1894,7 +1815,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Barkfläkt gran. Typiska hackspår.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1921,15 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120639644</v>
+        <v>120642799</v>
       </c>
       <c r="B13" t="n">
-        <v>78594</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1937,34 +1858,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Blekatjärnen, Blekatjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>470361</v>
+        <v>470404</v>
       </c>
       <c r="R13" t="n">
-        <v>7017017</v>
+        <v>7016956</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1996,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2006,7 +1932,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Hackspår i mindre gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2033,53 +1964,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120642865</v>
+        <v>120639815</v>
       </c>
       <c r="B14" t="n">
-        <v>98056</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Blekatjärnen, Blekatjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>470420</v>
+        <v>470329</v>
       </c>
       <c r="R14" t="n">
-        <v>7016945</v>
+        <v>7017021</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2108,7 +2043,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2118,7 +2053,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2145,15 +2080,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120641044</v>
+        <v>120643646</v>
       </c>
       <c r="B15" t="n">
-        <v>90679</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,37 +2091,46 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Blekatjärnen, Blekatjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>470279</v>
+        <v>470483</v>
       </c>
       <c r="R15" t="n">
-        <v>7017039</v>
+        <v>7016835</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2220,7 +2159,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2230,12 +2169,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På grov granlåga.</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2262,37 +2196,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120639815</v>
+        <v>7294892</v>
       </c>
       <c r="B16" t="n">
-        <v>57501</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>208249</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2300,24 +2229,39 @@
           <t>2</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Blekatjärnen, Blekatjärnen, Jmt</t>
+          <t>Blektjärn, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>470329</v>
+        <v>470465</v>
       </c>
       <c r="R16" t="n">
-        <v>7017021</v>
+        <v>7016813</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2341,22 +2285,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:55</t>
+          <t>2010-05-14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:55</t>
+          <t>2010-05-14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2371,70 +2305,85 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Anders Forsgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Anders Forsgren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Internationell Herptilinventering med Svensk bas</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120642799</v>
+        <v>7268890</v>
       </c>
       <c r="B17" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58815</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>208250</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Blekatjärnen, Blekatjärnen, Jmt</t>
+          <t>Blektjärn, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>470404</v>
+        <v>470465</v>
       </c>
       <c r="R17" t="n">
-        <v>7016956</v>
+        <v>7016813</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2458,84 +2407,88 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>14:33</t>
+          <t>2014-04-28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>14:33</t>
+          <t>2014-04-28</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Hackspår i mindre gran.</t>
+          <t>Lokal 020 för R. arvalis. Besökt redan på sent 70-tal men då utom speltid med negativt resultat då. Arten dock sedemera bekräftad, men litet känt om populationens storlek eller utveckling, de förefaller dock ha minskat i antal efter att först måsar och sedan en utterfamilj etablierade sig här. 2014 försökte jag få dom att spela med härmat spelljud.  De reagerade och en närmade sig, men inget svar. Bytte till temporaria, men ingen reaktion. Honor eller helt enkelt för kallt och blåsigt väder. Utan att få svar på spelljud så för observationen betecknas som osäker.  Ospontan: Möjlig mej ej bekräftad hybridpopulation.</t>
         </is>
       </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG17" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Vattenyta i kalkblekesjö</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Kalksten</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Limestone</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Anders Forsgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Anders Forsgren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Internationell Herptilinventering med Svensk bas</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120640899</v>
+        <v>120642865</v>
       </c>
       <c r="B18" t="n">
-        <v>97010</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2545,13 +2498,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>470279</v>
+        <v>470420</v>
       </c>
       <c r="R18" t="n">
-        <v>7017039</v>
+        <v>7016945</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2580,7 +2533,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2590,7 +2543,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2617,37 +2570,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120640856</v>
+        <v>120640899</v>
       </c>
       <c r="B19" t="n">
-        <v>79675</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2657,13 +2605,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>470308</v>
+        <v>470279</v>
       </c>
       <c r="R19" t="n">
-        <v>7017030</v>
+        <v>7017039</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2692,7 +2640,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2702,12 +2650,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt på gamla sälgar.</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2731,6 +2674,220 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120639552</v>
+      </c>
+      <c r="B20" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Blekatjärnen, Blekatjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>470404</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7017028</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120640895</v>
+      </c>
+      <c r="B21" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Blekatjärnen, Blekatjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>470279</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7017039</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39503-2024 artfynd.xlsx
+++ b/artfynd/A 39503-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120639689</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120641835</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120641044</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1095,6 +1115,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104036321</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120639644</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1309,6 +1339,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120641868</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1406,6 +1441,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101537654</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1518,6 +1558,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120640856</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1625,6 +1670,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120639534</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1727,6 +1777,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120448428</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1844,6 +1899,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120641824</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1961,6 +2021,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120642799</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2077,6 +2142,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120639815</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2193,6 +2263,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120643646</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2318,6 +2393,11 @@
           <t>Internationell Herptilinventering med Svensk bas</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7294892</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2460,6 +2540,11 @@
           <t>Internationell Herptilinventering med Svensk bas</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7268890</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2567,6 +2652,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120642865</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2674,6 +2764,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120640899</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2781,6 +2876,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120639552</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2888,8 +2988,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120640895</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>